--- a/www/terminologies/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/www/terminologies/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T14:36:40+00:00</t>
+    <t>2026-08-27T16:10:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/www/terminologies/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>retired</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T16:10:25+00:00</t>
+    <t>2026-09-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
